--- a/src/Apps/ExcelReport/Aloe.Apps.ExcelReportCli/ExcelReportTemplate.xlsx
+++ b/src/Apps/ExcelReport/Aloe.Apps.ExcelReportCli/ExcelReportTemplate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="96" documentId="11_31802F1733C7A0836B02CE998F682C9D7A7B838F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B568ECD-3766-4F82-A84F-601339C0F622}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="11_31802F1733C7A0836B02CE998F682C9D7A7B838F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{105BC4F9-0B07-49B7-9F8D-F3A0273E246C}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,6 +30,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={5941612C-2476-4C4D-AC2F-8C9BDAFD6606}</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{5941612C-2476-4C4D-AC2F-8C9BDAFD6606}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    コメントテスト</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
@@ -109,7 +127,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +193,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bernard MT Condensed"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Broadway"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cochocib Script Latin Pro"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="HGPSoeiKakugothicUB"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="UD Digi Kyokasho N-B"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -190,7 +233,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -474,48 +517,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -525,9 +594,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -537,16 +603,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -576,59 +699,68 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -905,6 +1037,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="髙田 和範" id="{C1DA2C03-2692-4DC0-9ADE-8E5730EAA79F}" userId="S::takada@prismed01.onmicrosoft.com::e1ca7a3c-e704-4f5a-8857-291741b402e1" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1202,8 +1340,16 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D2" dT="2026-03-12T12:38:30.99" personId="{C1DA2C03-2692-4DC0-9ADE-8E5730EAA79F}" id="{5941612C-2476-4C4D-AC2F-8C9BDAFD6606}">
+    <text>コメントテスト</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:Y26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -1212,46 +1358,52 @@
   <sheetData>
     <row r="1" spans="2:25" ht="15.75"/>
     <row r="2" spans="2:25" ht="15.75">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="15"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="58">
+        <f ca="1">NOW()</f>
+        <v>46093.903370949076</v>
+      </c>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="7"/>
     </row>
     <row r="3" spans="2:25" ht="15.75">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="E3" s="61" t="str">
+        <f>REPT("0123456789",  10)</f>
+        <v>0123456789012345678901234567890123456789012345678901234567890123456789012345678901234567890123456789</v>
+      </c>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -1265,14 +1417,14 @@
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
-      <c r="Y3" s="17"/>
+      <c r="Y3" s="8"/>
     </row>
     <row r="4" spans="2:25" ht="15.75">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1293,44 +1445,44 @@
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="17"/>
+      <c r="Y4" s="8"/>
     </row>
     <row r="5" spans="2:25" ht="15.75">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="18"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="9"/>
     </row>
     <row r="6" spans="2:25" ht="15.75">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="13"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -1349,17 +1501,17 @@
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="17"/>
+      <c r="Y6" s="8"/>
     </row>
     <row r="7" spans="2:25" ht="15.75">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="13"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -1377,18 +1529,18 @@
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="17"/>
+      <c r="Y7" s="8"/>
     </row>
     <row r="8" spans="2:25" ht="15.75">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="13"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1405,19 +1557,19 @@
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-      <c r="Y8" s="17"/>
+      <c r="Y8" s="8"/>
     </row>
     <row r="9" spans="2:25" ht="15.75">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="3"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="13"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1433,21 +1585,21 @@
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
-      <c r="Y9" s="17"/>
+      <c r="Y9" s="8"/>
     </row>
     <row r="10" spans="2:25" ht="15.75">
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="4"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -1461,22 +1613,22 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
-      <c r="Y10" s="17"/>
+      <c r="Y10" s="8"/>
     </row>
     <row r="11" spans="2:25" ht="15.75">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="4"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="2"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -1489,22 +1641,22 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-      <c r="Y11" s="17"/>
+      <c r="Y11" s="8"/>
     </row>
     <row r="12" spans="2:25" ht="15.75">
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="29"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="39"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -1517,23 +1669,23 @@
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
-      <c r="Y12" s="17"/>
+      <c r="Y12" s="8"/>
     </row>
     <row r="13" spans="2:25" ht="15.75">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="32"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="42"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
@@ -1545,24 +1697,24 @@
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-      <c r="Y13" s="17"/>
+      <c r="Y13" s="8"/>
     </row>
     <row r="14" spans="2:25" ht="15.75">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="35"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="18"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -1573,25 +1725,25 @@
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
-      <c r="Y14" s="17"/>
+      <c r="Y14" s="8"/>
     </row>
     <row r="15" spans="2:25" ht="15.75">
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="38"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="21"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
@@ -1601,26 +1753,26 @@
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
-      <c r="Y15" s="17"/>
+      <c r="Y15" s="8"/>
     </row>
     <row r="16" spans="2:25" ht="15.75">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="41"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="24"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -1629,27 +1781,27 @@
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-      <c r="Y16" s="17"/>
+      <c r="Y16" s="8"/>
     </row>
     <row r="17" spans="2:25" ht="15.75">
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="44"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="27"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -1657,240 +1809,248 @@
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
-      <c r="Y17" s="17"/>
+      <c r="Y17" s="8"/>
     </row>
     <row r="18" spans="2:25" ht="15.75">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
-      <c r="P18" s="46"/>
-      <c r="Q18" s="46"/>
-      <c r="R18" s="47"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="30"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
-      <c r="Y18" s="17"/>
+      <c r="Y18" s="8"/>
     </row>
     <row r="19" spans="2:25" ht="15.75">
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="49"/>
-      <c r="R19" s="49"/>
-      <c r="S19" s="50"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="33"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-      <c r="Y19" s="17"/>
+      <c r="Y19" s="8"/>
     </row>
     <row r="20" spans="2:25" ht="15.75">
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="10"/>
-      <c r="U20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="4"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
-      <c r="Y20" s="17"/>
+      <c r="Y20" s="8"/>
     </row>
     <row r="21" spans="2:25" ht="15.75">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="4"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="45"/>
+      <c r="V21" s="2"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-      <c r="Y21" s="17"/>
+      <c r="Y21" s="8"/>
     </row>
     <row r="22" spans="2:25" ht="15.75">
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="3"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="47"/>
+      <c r="N22" s="47"/>
+      <c r="O22" s="47"/>
+      <c r="P22" s="47"/>
+      <c r="Q22" s="47"/>
+      <c r="R22" s="47"/>
+      <c r="S22" s="47"/>
+      <c r="T22" s="47"/>
+      <c r="U22" s="47"/>
+      <c r="V22" s="48"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
-      <c r="Y22" s="17"/>
-    </row>
-    <row r="23" spans="2:25" ht="15.75">
-      <c r="B23" s="16" t="s">
+      <c r="Y22" s="8"/>
+    </row>
+    <row r="23" spans="2:25" ht="17.25">
+      <c r="B23" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="3"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="50"/>
+      <c r="Q23" s="50"/>
+      <c r="R23" s="50"/>
+      <c r="S23" s="50"/>
+      <c r="T23" s="50"/>
+      <c r="U23" s="50"/>
+      <c r="V23" s="50"/>
+      <c r="W23" s="51"/>
       <c r="X23" s="1"/>
-      <c r="Y23" s="17"/>
+      <c r="Y23" s="8"/>
     </row>
     <row r="24" spans="2:25" ht="15.75">
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="17"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
+      <c r="R24" s="53"/>
+      <c r="S24" s="53"/>
+      <c r="T24" s="53"/>
+      <c r="U24" s="53"/>
+      <c r="V24" s="53"/>
+      <c r="W24" s="53"/>
+      <c r="X24" s="54"/>
+      <c r="Y24" s="8"/>
     </row>
     <row r="25" spans="2:25" ht="15.75">
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="22"/>
-      <c r="S25" s="22"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="22"/>
-      <c r="X25" s="22"/>
-      <c r="Y25" s="23"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="56"/>
+      <c r="P25" s="56"/>
+      <c r="Q25" s="56"/>
+      <c r="R25" s="56"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="56"/>
+      <c r="U25" s="56"/>
+      <c r="V25" s="56"/>
+      <c r="W25" s="56"/>
+      <c r="X25" s="56"/>
+      <c r="Y25" s="57"/>
     </row>
     <row r="26" spans="2:25" ht="15.75"/>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="B20:T20"/>
-    <mergeCell ref="B21:U21"/>
-    <mergeCell ref="B22:V22"/>
-    <mergeCell ref="B23:W23"/>
-    <mergeCell ref="B24:X24"/>
+  <mergeCells count="25">
+    <mergeCell ref="E2:K2"/>
+    <mergeCell ref="E3:K3"/>
+    <mergeCell ref="B13:M13"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="B11:K11"/>
+    <mergeCell ref="B12:L12"/>
     <mergeCell ref="B25:Y25"/>
     <mergeCell ref="B14:N14"/>
     <mergeCell ref="B15:O15"/>
@@ -1898,19 +2058,14 @@
     <mergeCell ref="B17:Q17"/>
     <mergeCell ref="B18:R18"/>
     <mergeCell ref="B19:S19"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:J10"/>
-    <mergeCell ref="B11:K11"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="B13:M13"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B20:T20"/>
+    <mergeCell ref="B21:U21"/>
+    <mergeCell ref="B22:V22"/>
+    <mergeCell ref="B23:W23"/>
+    <mergeCell ref="B24:X24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>